--- a/referências.xlsx
+++ b/referências.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="1614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3256" uniqueCount="1622">
   <si>
     <t>Iata Code</t>
   </si>
@@ -4882,6 +4882,30 @@
   </si>
   <si>
     <t>SBME</t>
+  </si>
+  <si>
+    <t>JPR</t>
+  </si>
+  <si>
+    <t>Ji-Paraná</t>
+  </si>
+  <si>
+    <t>SBJI</t>
+  </si>
+  <si>
+    <t>GBE</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>Gaborone</t>
+  </si>
+  <si>
+    <t>FBSK</t>
+  </si>
+  <si>
+    <t>Botsuana</t>
   </si>
 </sst>
 </file>
@@ -8776,7 +8800,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I289"/>
+  <dimension ref="A1:I291"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -16391,6 +16415,60 @@
         <v>1612</v>
       </c>
     </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A290" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="H290" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I290" s="2" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A291" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I291" s="2" t="s">
+        <v>1620</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I286"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
